--- a/en/downloads/data-excel/3.8.2.xlsx
+++ b/en/downloads/data-excel/3.8.2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC62FF88-2201-4D56-8633-54166A7DCEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="855" windowWidth="17400" windowHeight="14610" tabRatio="599"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ЦУР 3.8.2 &gt;10%" sheetId="2" r:id="rId1"/>
@@ -465,11 +466,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="###0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,14 +581,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF444444"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
@@ -612,6 +606,33 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF444444"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -651,95 +672,99 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
+    <cellStyle name="Normal 17" xfId="5" xr:uid="{F41460F5-C1AA-4FB2-8259-0C8D50298A78}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="3"/>
-    <cellStyle name="Обычный 3" xfId="2"/>
-    <cellStyle name="Обычный_Лист1" xfId="1"/>
-    <cellStyle name="Обычный_Лист2" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный_Лист1" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный_Лист2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1050,14 +1075,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="35.28515625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="7" customWidth="1"/>
-    <col min="5" max="9" width="7.85546875" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="3" width="35.28515625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" style="6" customWidth="1"/>
+    <col min="5" max="9" width="7.85546875" style="6" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="26"/>
+    <col min="11" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1075,1251 +1101,1372 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" s="17" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="J1" s="31"/>
+    </row>
+    <row r="2" spans="1:10" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" s="8" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="J3" s="29"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="18">
         <v>2018</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="18">
         <v>2019</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="17">
         <v>2020</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="18">
         <v>2021</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="18">
         <v>2022</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="18">
         <v>2023</v>
       </c>
+      <c r="J4" s="18">
+        <v>2024</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="19">
         <v>5.1365548709942459</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="19">
         <v>5.273268512156954</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="19">
         <v>4.8236985785117623</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="19">
         <v>4.0517625380241995</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="19">
         <v>4.5805157677547461</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="19">
         <v>4.7416174744126858</v>
       </c>
+      <c r="J5" s="27">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="20">
         <v>4.161283749327457</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="20">
         <v>4.8372460048938173</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="20">
         <v>4.7861397487070043</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="20">
         <v>3.8372007252778246</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="20">
         <v>4.1921749611988233</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="20">
         <v>5.9926953992848642</v>
       </c>
+      <c r="J7" s="30">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="20">
         <v>5.6789922604826257</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="20">
         <v>5.5179055441701488</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="20">
         <v>4.8451036393496283</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="20">
         <v>4.1792839379285898</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="20">
         <v>4.8064535284779586</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="20">
         <v>4.0165298959233224</v>
       </c>
+      <c r="J8" s="30">
+        <v>4.0999999999999996</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="30"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="20">
         <v>4.8572833842908052</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="20">
         <v>4.8488823527249991</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="20">
         <v>4.5782646914301415</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="20">
         <v>3.6703940408331857</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="20">
         <v>4.3305847274139095</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="20">
         <v>4.4225160868674385</v>
       </c>
+      <c r="J10" s="30">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="20">
         <v>5.3854772328911729</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="20">
         <v>5.6496566065690903</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="20">
         <v>5.0446245420263285</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="20">
         <v>4.3941034101107039</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="20">
         <v>4.8055246823673139</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="20">
         <v>5.0327040512455437</v>
       </c>
+      <c r="J11" s="30">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="30"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="20">
         <v>4.0797805562332483</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="20">
         <v>4.2112035665437411</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="20">
         <v>1.5127220831294372</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="20">
         <v>1.7166656655506132</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="20">
         <v>1.5415652552916528</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="20">
         <v>2.1614606884041336</v>
       </c>
+      <c r="J13" s="30">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="20">
         <v>2.9846504867725878</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="20">
         <v>1.4548947685200386</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="20">
         <v>0.25028060636164384</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="20">
         <v>0</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="20">
         <v>0.1686711361337058</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="20">
         <v>2.2316871848117805</v>
       </c>
+      <c r="J14" s="30">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="20">
         <v>3.038796849349247</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="20">
         <v>2.7788994886972853</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="20">
         <v>2.0195100556590444</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="20">
         <v>2.5766819236935254</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="20">
         <v>2.7154857574876314</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="20">
         <v>1.9131665905589259</v>
       </c>
+      <c r="J15" s="30">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="20">
         <v>10.512053716998178</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="20">
         <v>9.5246125761026157</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="20">
         <v>8.2284078682166939</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="20">
         <v>8.630632269964531</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="20">
         <v>5.7557045351365979</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="20">
         <v>9.5882183582798746</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+      <c r="J16" s="30">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="20">
         <v>5.22637344294942</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="20">
         <v>6.3689011927205996</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="20">
         <v>5.9682627880509127</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="20">
         <v>4.8271537364642594</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="20">
         <v>6.5369594131892059</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="20">
         <v>3.2295717806957898</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="J17" s="30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="20">
         <v>1.8937640406124039</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="20">
         <v>0.77335249662342942</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="20">
         <v>0.27748968426157544</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="20">
         <v>1.0003750599820724</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="20">
         <v>1.2265086836006607</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="20">
         <v>1.6722862697404342</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="J18" s="30">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="20">
         <v>10.410449506890966</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="20">
         <v>11.892504521965122</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="20">
         <v>12.337537993618204</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="20">
         <v>10.258705210076251</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="20">
         <v>10.614013094527648</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="20">
         <v>10.854271137678044</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="J19" s="30">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="20">
         <v>2.8321486117654171</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="20">
         <v>3.0035168563965704</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="20">
         <v>5.326268491180068</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="20">
         <v>3.1702943714271035</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="20">
         <v>4.103090426778941</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="20">
         <v>3.2022617935387316</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
+      <c r="J20" s="30">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="20">
         <v>7.7751687468604169</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="20">
         <v>8.6310891769001188</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="20">
         <v>4.0726557712311511</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="20">
         <v>5.5075392520073958</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="20">
         <v>5.448582749899451</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="20">
         <v>13.295994264899148</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
+      <c r="J21" s="30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="30"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="20">
         <v>4.2324156841930964</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="20">
         <v>4.4602121113688549</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="20">
         <v>3.8427985472090285</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="20">
         <v>3.198746417652246</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="20">
         <v>3.5922054954117804</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="20">
         <v>4.0166829948717906</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
+      <c r="J23" s="30">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="20">
         <v>4.2711414831580168</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="20">
         <v>3.8240312593685961</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="20">
         <v>3.4544699733496422</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="20">
         <v>3.1413478591905677</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="20">
         <v>3.8037768728653667</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="20">
         <v>3.3691436064992599</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
+      <c r="J24" s="30">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="20">
         <v>3.9731129021199734</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="20">
         <v>4.1561425797317879</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="20">
         <v>3.564012181640706</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="20">
         <v>2.1668725995454992</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="20">
         <v>3.5678124374853653</v>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="20">
         <v>3.4599551825810391</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="24" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
+      <c r="J25" s="30">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="20">
         <v>4.7549613134738102</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="20">
         <v>4.7622901843292755</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="20">
         <v>3.9844992034848765</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="20">
         <v>3.5660468261488774</v>
       </c>
-      <c r="H26" s="23">
+      <c r="H26" s="20">
         <v>3.7178576442254121</v>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="20">
         <v>4.3812573669977972</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="24" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
+      <c r="J26" s="30">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="20">
         <v>11.574276475965425</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="20">
         <v>12.473761994301055</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="20">
         <v>12.891104865504044</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="20">
         <v>10.874084630363939</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="20">
         <v>10.873905455753114</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="20">
         <v>10.406702599782424</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="10" t="s">
+      <c r="J27" s="30">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="30"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="20">
         <v>4.3975617064312544</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="20">
         <v>3.9177429723003194</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="20">
         <v>3.7531523838907845</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="20">
         <v>3.4418074719591099</v>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="20">
         <v>3.7773202952354197</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="20">
         <v>3.6934359958808138</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
+      <c r="J29" s="30">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="20">
         <v>5.8866723877626717</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="20">
         <v>7.088964913662041</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="20">
         <v>7.2257210156644067</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="20">
         <v>5.2216037598371683</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="20">
         <v>5.873604901266761</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="20">
         <v>6.699884400782266</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
+      <c r="J30" s="30">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="20">
         <v>5.1116207511076865</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="20">
         <v>4.6498635254717309</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="20">
         <v>3.6638698535729537</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="20">
         <v>3.4468699964433127</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="20">
         <v>4.3033413766281932</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="20">
         <v>4.1901343228341537</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
+      <c r="J31" s="30">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="20">
         <v>7.3468915514958208</v>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="20">
         <v>9.1997897055842355</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="20">
         <v>7.869041675845982</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="20">
         <v>6.5058462291501309</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="20">
         <v>6.5452144828622485</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="20">
         <v>7.8073346572319258</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
+      <c r="J32" s="30">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="20">
         <v>4.906987360717042</v>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="20">
         <v>5.2297241014762994</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="20">
         <v>6.3778015929400409</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="20">
         <v>4.9745168726134628</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="20">
         <v>4.7832979287075723</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="20">
         <v>4.7686369009707859</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="12" t="s">
+      <c r="J33" s="30">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
-    </row>
-    <row r="35" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="13" t="s">
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="30"/>
+    </row>
+    <row r="35" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="20">
         <v>2.7721763526193408</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="20">
         <v>2.7132847449681328</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="20">
         <v>2.3028025098978642</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="20">
         <v>2.734395135594478</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="20">
         <v>4.1018123425412432</v>
       </c>
-      <c r="I35" s="23">
+      <c r="I35" s="20">
         <v>3.5908002627550815</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="13" t="s">
+      <c r="J35" s="30">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="20">
         <v>4.834968995921284</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="20">
         <v>4.509004610704447</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="20">
         <v>4.9802795126477468</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="20">
         <v>3.5549422469836074</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="20">
         <v>3.7948675346263028</v>
       </c>
-      <c r="I36" s="23">
+      <c r="I36" s="20">
         <v>5.447609067019787</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="13" t="s">
+      <c r="J36" s="30">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="20">
         <v>5.195938174739533</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="20">
         <v>5.0532056543323698</v>
       </c>
-      <c r="F37" s="23">
+      <c r="F37" s="20">
         <v>5.2104967289787769</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="20">
         <v>3.7231746992023198</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="20">
         <v>4.3620789960622339</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I37" s="20">
         <v>5.7926422894397982</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="13" t="s">
+      <c r="J37" s="30">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="20">
         <v>7.8107723916289853</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="20">
         <v>7.9018100206967876</v>
       </c>
-      <c r="F38" s="23">
+      <c r="F38" s="20">
         <v>4.2816595947797538</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="20">
         <v>5.0922691439865231</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="20">
         <v>5.4263728003623388</v>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="20">
         <v>3.8217587687047279</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
+      <c r="J38" s="30">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="20">
         <v>5.0726527812098938</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="20">
         <v>6.193867275232309</v>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="20">
         <v>7.3363175599298653</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="20">
         <v>5.1538724101167617</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="20">
         <v>5.2159726377746969</v>
       </c>
-      <c r="I39" s="23">
+      <c r="I39" s="20">
         <v>5.0531867893720213</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="12" t="s">
+      <c r="J39" s="30">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-    </row>
-    <row r="41" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="30"/>
+    </row>
+    <row r="41" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="20">
         <v>9.2486584084639638</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="20">
         <v>9.8292336259867135</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="20">
         <v>10.58526371493317</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="20">
         <v>8.0088000599773839</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="20">
         <v>7.5957774611229461</v>
       </c>
-      <c r="I41" s="23">
+      <c r="I41" s="20">
         <v>11.143652618963991</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="15" t="s">
+      <c r="J41" s="30">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="20">
         <v>4.3844791127035725</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="20">
         <v>4.3946283256662504</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="20">
         <v>3.6885469475506061</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="20">
         <v>3.2710758282114001</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="20">
         <v>3.9668761578150442</v>
       </c>
-      <c r="I42" s="23">
+      <c r="I42" s="20">
         <v>3.453395511091423</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="15" t="s">
+      <c r="J42" s="30">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="20">
         <v>3.1441644943520588</v>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="20">
         <v>3.1818267972184562</v>
       </c>
-      <c r="F43" s="23">
+      <c r="F43" s="20">
         <v>2.8059036409912181</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="20">
         <v>2.1309244977337873</v>
       </c>
-      <c r="H43" s="23">
+      <c r="H43" s="20">
         <v>2.4796125498542425</v>
       </c>
-      <c r="I43" s="23">
+      <c r="I43" s="20">
         <v>3.1878249769520886</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" ht="24" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
+      <c r="J43" s="30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+      <c r="A44" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="20">
         <v>9.144599830433414</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="20">
         <v>9.1119305773499697</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="20">
         <v>8.1842248566856668</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="20">
         <v>7.0515551649177857</v>
       </c>
-      <c r="H44" s="23">
+      <c r="H44" s="20">
         <v>7.8800680526649458</v>
       </c>
-      <c r="I44" s="23">
+      <c r="I44" s="20">
         <v>7.0669416483382248</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" ht="24" x14ac:dyDescent="0.2">
-      <c r="A45" s="15" t="s">
+      <c r="J44" s="30">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+      <c r="A45" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="20">
         <v>22.59220852359611</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="20">
         <v>26.629731364017598</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F45" s="20">
         <v>31.340493557009605</v>
       </c>
-      <c r="G45" s="23">
+      <c r="G45" s="20">
         <v>26.662226281252554</v>
       </c>
-      <c r="H45" s="23">
+      <c r="H45" s="20">
         <v>22.312812234357711</v>
       </c>
-      <c r="I45" s="23">
+      <c r="I45" s="20">
         <v>21.878441980373022</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
+      <c r="J45" s="30">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D46" s="23">
+      <c r="D46" s="20">
         <v>2.4047967026299291</v>
       </c>
-      <c r="E46" s="23">
+      <c r="E46" s="20">
         <v>2.0827845527203261</v>
       </c>
-      <c r="F46" s="23">
+      <c r="F46" s="20">
         <v>2.7583224955402175</v>
       </c>
-      <c r="G46" s="23">
+      <c r="G46" s="20">
         <v>1.2346203013541339</v>
       </c>
-      <c r="H46" s="23">
+      <c r="H46" s="20">
         <v>1.4349327367500571</v>
       </c>
-      <c r="I46" s="23">
+      <c r="I46" s="20">
         <v>1.9802187319904174</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
+      <c r="J46" s="30">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="20">
         <v>0</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="20">
         <v>0</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="20">
         <v>6.2641406076676089</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="20">
         <v>0.60384830009485124</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H47" s="20">
         <v>1.171406368174436</v>
       </c>
-      <c r="I47" s="23">
+      <c r="I47" s="20">
         <v>1.1955030353910923</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
+      <c r="J47" s="30">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="30"/>
     </row>
     <row r="49" spans="1:9" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2328,16 +2475,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="34.5703125" style="7" customWidth="1"/>
-    <col min="4" max="7" width="8.140625" style="7" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="3" width="34.5703125" style="6" customWidth="1"/>
+    <col min="4" max="7" width="8.140625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="3" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>137</v>
       </c>
@@ -2352,1009 +2499,1130 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" s="8" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" s="7" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="17">
         <v>2020</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="18">
         <v>2021</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="18">
         <v>2022</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="18">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
+      <c r="H4" s="18">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="19">
         <v>0.81146561584551613</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="19">
         <v>0.85840547506881848</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="19">
         <v>0.76629816720225807</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="19">
         <v>0.61301606643531215</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+      <c r="H5" s="27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="30"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="20">
         <v>0.74901739833193293</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="20">
         <v>0.59444179865667479</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="20">
         <v>0.30786487275871099</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="20">
         <v>0.67017324840695591</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="H7" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="20">
         <v>0.84705532676152528</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="20">
         <v>1.0152880867000602</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="20">
         <v>1.0330159322142223</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="20">
         <v>0.57988946269212105</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
+      <c r="H8" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="30"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="20">
         <v>0.75908011363065186</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="20">
         <v>0.85555163973020354</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="20">
         <v>0.77136653985651615</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="20">
         <v>0.58466633549307523</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="H10" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="20">
         <v>0.85862013753209676</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="20">
         <v>0.86096726107319721</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="20">
         <v>0.76173519243837673</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="20">
         <v>0.63887689454887686</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="H11" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="30"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="20">
         <v>0.51093615899626565</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="20">
         <v>0.55478542509672846</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="20">
         <v>6.2620953042709829E-2</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="20">
         <v>0.40452960207020544</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="H13" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="20">
         <v>0.25028060636164384</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="20">
         <v>0</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="20">
         <v>0</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="20">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="H14" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="20">
         <v>0.11943828072895522</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="20">
         <v>0.22533849368225239</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="20">
         <v>0.37896071107072299</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="20">
         <v>0.6115686311116042</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+      <c r="H15" s="30">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="20">
         <v>1.360843708487627</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="20">
         <v>1.0747895514133363</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="20">
         <v>1.1872729806124076</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="20">
         <v>0.87919314325325604</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+      <c r="H16" s="30">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="20">
         <v>1.3579414933945704</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="20">
         <v>1.7220976040023868</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="20">
         <v>2.0442321121370908</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="20">
         <v>5.8103171351237326E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="H17" s="30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="20">
         <v>0</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="20">
         <v>0.33342951742417087</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="20">
         <v>1.0485744117678895</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="20">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="H18" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="20">
         <v>1.1075132498102238</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="20">
         <v>1.355995451397793</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="20">
         <v>1.0168058774498683</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="20">
         <v>2.1596513444043537</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="H19" s="30">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="20">
         <v>1.1858782707686208</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="20">
         <v>0.3273968036619474</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="20">
         <v>0.13878209486745066</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="20">
         <v>0.45632109736560028</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
+      <c r="H20" s="30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="20">
         <v>0.27402315976522723</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="20">
         <v>2.481448752388697</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="20">
         <v>0.74521429286708296</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="20">
         <v>1.5839114843370221</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
+      <c r="H21" s="30">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="30"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="20">
         <v>0.54361395112599353</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="20">
         <v>0.81938701585208418</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="20">
         <v>0.68376383230755577</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="20">
         <v>0.34844063241922946</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
+      <c r="H23" s="30">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="20">
         <v>0.66143055050033617</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="20">
         <v>0.70887612901276098</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="20">
         <v>0.58789439430618551</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="20">
         <v>0.21734898860075494</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
+      <c r="H24" s="30">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="20">
         <v>0.54716151841736216</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="20">
         <v>0.31227566185816458</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="20">
         <v>0.69890991732273011</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="20">
         <v>0.52651937218239853</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="24" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
+      <c r="H25" s="30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="24" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="20">
         <v>0.78121972379583049</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="20">
         <v>0.82472737861940448</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="20">
         <v>0.64599088802547744</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="20">
         <v>0.5239561153853679</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="24" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
+      <c r="H26" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="24" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="20">
         <v>1.9025450392608747</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="20">
         <v>2.0895422260230698</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="20">
         <v>1.5918453280297447</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="20">
         <v>1.8731413229766682</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="10" t="s">
+      <c r="H27" s="30">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="30"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="20">
         <v>0.61405219015335211</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="20">
         <v>0.76510172723135972</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="20">
         <v>0.5681380520645678</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="20">
         <v>0.35696493636053289</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
+      <c r="H29" s="30">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="20">
         <v>1.4935822119861977</v>
       </c>
-      <c r="E30" s="23">
+      <c r="E30" s="20">
         <v>1.9004663044455012</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="20">
         <v>1.6646885118176407</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="20">
         <v>1.1163483265140155</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
+      <c r="H30" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="20">
         <v>0.7318847615137124</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="20">
         <v>0.75771350970915463</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="20">
         <v>0.76967604278695623</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="20">
         <v>0.56721853988264148</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
+      <c r="H31" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="20">
         <v>1.070197900897315</v>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="20">
         <v>1.0999299729101983</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="20">
         <v>0.89356691349245454</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="20">
         <v>1.219068724525928</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
+      <c r="H32" s="30">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="20">
         <v>0.90762452275932815</v>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="20">
         <v>0.62357913889862282</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="20">
         <v>0.41670075008795943</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="20">
         <v>0.59703885920348987</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="12" t="s">
+      <c r="H33" s="30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-    </row>
-    <row r="35" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="13" t="s">
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="30"/>
+    </row>
+    <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="20">
         <v>0.37106205547354881</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="20">
         <v>0.52502882125193373</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="20">
         <v>0.44390867297579994</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="20">
         <v>7.9781219996398423E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="13" t="s">
+      <c r="H35" s="30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="20">
         <v>0.36144211000814963</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="20">
         <v>0.17079567926485234</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="20">
         <v>0.10171731643109012</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="20">
         <v>0.69784455802986878</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="13" t="s">
+      <c r="H36" s="30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="20">
         <v>0.19151277575068393</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="20">
         <v>0.38799965783834717</v>
       </c>
-      <c r="F37" s="23">
+      <c r="F37" s="20">
         <v>0.30732026165275794</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="20">
         <v>0.58549904936845942</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="13" t="s">
+      <c r="H37" s="30">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="20">
         <v>1.2512568525756129</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="20">
         <v>1.2263923208584242</v>
       </c>
-      <c r="F38" s="23">
+      <c r="F38" s="20">
         <v>1.9101046394997536</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="20">
         <v>0.60544403350649856</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
+      <c r="H38" s="30">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="20">
         <v>1.8820450768621539</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="20">
         <v>1.9804931347232968</v>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="20">
         <v>1.0661553197499942</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="20">
         <v>1.0964200013706473</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="12" t="s">
+      <c r="H39" s="30">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-    </row>
-    <row r="41" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="30"/>
+    </row>
+    <row r="41" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="20">
         <v>1.5751122718498423</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="20">
         <v>1.2178230863031267</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="20">
         <v>1.0340189637057775</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="20">
         <v>2.3211447620047418</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="15" t="s">
+      <c r="H41" s="30">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="20">
         <v>0.66101088236318273</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="20">
         <v>0.78749572230388454</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="20">
         <v>0.71181397914637767</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="20">
         <v>0.26930522259769263</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="15" t="s">
+      <c r="H42" s="30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="20">
         <v>0.83982758534555679</v>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="20">
         <v>0.5045934659976935</v>
       </c>
-      <c r="F43" s="23">
+      <c r="F43" s="20">
         <v>0.55478103076355156</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="20">
         <v>0.35068361234497264</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="24" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
+      <c r="H43" s="30">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="24" x14ac:dyDescent="0.2">
+      <c r="A44" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="20">
         <v>0.76423031852497103</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="20">
         <v>1.4109573476657906</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="20">
         <v>1.0984942649984508</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="20">
         <v>1.0056090272704485</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="15" t="s">
+      <c r="H44" s="30">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="20">
         <v>6.9630699556693765</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="20">
         <v>4.9391855240833769</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F45" s="20">
         <v>3.2216631087190186</v>
       </c>
-      <c r="G45" s="23">
+      <c r="G45" s="20">
         <v>5.7043446461854845</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
+      <c r="H45" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D46" s="23">
+      <c r="D46" s="20">
         <v>0.46315485344071838</v>
       </c>
-      <c r="E46" s="23">
+      <c r="E46" s="20">
         <v>0.12232205671834719</v>
       </c>
-      <c r="F46" s="23">
+      <c r="F46" s="20">
         <v>0.10291558073604964</v>
       </c>
-      <c r="G46" s="23">
+      <c r="G46" s="20">
         <v>5.3513965452919969E-2</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
+      <c r="H46" s="30">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="20">
         <v>0</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="20">
         <v>0</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="20">
         <v>0</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="20">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-    </row>
-    <row r="49" spans="1:7" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A49" s="26" t="s">
+      <c r="H47" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="21"/>
+    </row>
+    <row r="49" spans="1:8" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A49" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
